--- a/光伏配储项目/电价数据/2026/斗门站.xlsx
+++ b/光伏配储项目/电价数据/2026/斗门站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5544600000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.52978</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.25327</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.45326</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.59392</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.6809</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.67093</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.9427300000000001</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.92832</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.71054</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1.7102</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.72064</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.92161</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.69207</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1.70223</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.74082</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1.71424</v>
+      </c>
+      <c r="V117" t="n">
+        <v>1.02605</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.69931</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.95062</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.70134</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1.70133</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>1.03701</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.72501</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.79444</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.89852</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.70252</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.47757</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.76678</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.79016</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40652</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.06441</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.05532</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.14726</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.76406</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7321599999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.51142</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.79649</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.99962</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.36213</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.53415</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7944199999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.43174</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.8028099999999999</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.7734500000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.97435</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.9372999999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.08804</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.36774</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.2394</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.29212</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7543500000000001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.27136</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.20715</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10978</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.26635</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.55602</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.42158</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.29727</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.50917</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.35394</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.2686</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.45105</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.39047</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.32322</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.82337</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47925</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42191</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.20135</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.0495</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18522</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5176000000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1.01826</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.92118</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.9925900000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.8997200000000001</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.8906499999999999</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1.10604</v>
+      </c>
+      <c r="U118" t="n">
+        <v>1.00907</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.99885</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.99881</v>
+      </c>
+      <c r="X118" t="n">
+        <v>1.00949</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.96384</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>1.04107</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.45165</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.99675</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.89035</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.96882</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.85256</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.79825</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.97192</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.18385</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.8092200000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.1357</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.0688</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.03585</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7344700000000001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.55863</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.58285</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.70587</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.21718</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.27858</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.53064</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.20959</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.68463</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09784</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.85598</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.28924</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.18221</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.30218</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62785</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.65799</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57827</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6293</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.22908</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.21567</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.22293</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.21558</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.01404</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18227</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.19747</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19584</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67849</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.21164</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20878</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.2841</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.58271</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.50262</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.21645</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50536</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26727</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.76112</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7635</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91367</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33342</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.90947</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.22573</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.11818</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.77791</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.93199</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.8004600000000001</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.32282</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1.31285</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1.2435</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.99194</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1.28305</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1.01984</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1.33556</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.82097</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.93371</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.78324</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.95355</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>1.01488</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.91671</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>1.01212</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.00027</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.8664700000000001</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.7133999999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8430700000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.12471</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.88481</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7754800000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.71836</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.61137</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6409400000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.75186</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.19196</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.5759</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.70424</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.20294</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.69047</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19883</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.21212</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.81512</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.98751</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.21503</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.21461</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.91432</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56472</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.68196</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.19746</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.06269</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.21281</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.45826</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.30023</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.21102</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22632</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21631</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.46584</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.30189</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.31619</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.67801</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.23302</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.22921</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.08258</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.11262</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.13348</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.11955</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.25238</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.20542</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.29548</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.03477</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.77591</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.73358</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.26423</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1.14495</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.12499</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1.09896</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1.26666</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.94716</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1.22178</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.02583</v>
+      </c>
+      <c r="N120" t="n">
+        <v>1.31399</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1.32958</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1.26058</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.99279</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1.00039</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.68641</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.8454700000000001</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.6966100000000001</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.62358</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>1.04227</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.9882300000000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1.23922</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>1.01506</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.90019</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.8497100000000001</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.61283</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.69135</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72678</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9457000000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.20672</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.35081</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.87226</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.59313</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.67489</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9166599999999999</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.9056799999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.19947</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.45022</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.78166</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.00047</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.26424</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.7171799999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.11669</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.53355</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.49546</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.67592</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.03691</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.1366</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.2723</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.21088</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.11489</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.02818</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03871</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1.00266</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.31278</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.49078</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.82226</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.39539</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.24998</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.87283</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.11874</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.19625</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.13899</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.20251</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.2977</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.35699</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.20228</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.31121</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.21007</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19402</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18613</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.22684</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.2429</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.22866</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.20553</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7499400000000001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.53495</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.75475</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32212</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.75239</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.5019400000000001</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48723</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.5136499999999999</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.5332899999999999</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46815</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43611</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46565</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.7329199999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.86707</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.62906</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.71778</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.74336</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8646200000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.72139</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.56264</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5511699999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.6061599999999999</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.48184</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.10816</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55848</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.49552</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.52759</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.47011</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.65601</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5160800000000001</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49573</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49867</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.6138400000000001</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.51634</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.5147699999999999</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49348</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34444</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.2294</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.00802</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.02287</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.60268</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.94872</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1.06867</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.93747</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1.06908</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1.10461</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.10628</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.7122</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1.08886</v>
+      </c>
+      <c r="P122" t="n">
+        <v>1.08795</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1.10782</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1.1083</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1.1077</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.28184</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08449</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04435</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04631</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00383</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04515</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.43298</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>1.00789</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>1.07247</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>1.04696</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1.07228</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1.07264</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33466</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.9545800000000001</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.77313</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.91162</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.70098</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.67508</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6922200000000001</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.77549</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.9767100000000001</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.42151</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48535</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7525599999999999</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.7559400000000001</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.92259</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.76118</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.55247</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48613</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45966</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09734000000000001</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.7502000000000001</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.75862</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.66064</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6184500000000001</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48071</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.74421</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79188</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.79413</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6146200000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.75905</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.03556</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.44069</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.86788</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.47095</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.36609</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.8209</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.41594</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.07258</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.43632</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.79645</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.47332</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7919299999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8012699999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78574</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87926</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5028</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41242</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46103</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21953</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5414800000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1.02117</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1.02581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1.04816</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.03794</v>
+      </c>
+      <c r="N124" t="n">
+        <v>1.03154</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.91247</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1.03011</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1.05263</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.87388</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.81635</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.88518</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1.07392</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>1.10692</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>1.09438</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>1.09745</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>1.10083</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>1.06319</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1.09993</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.97078</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.8758400000000001</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.81638</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6002799999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5652200000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66727</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07739</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.65078</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.51144</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57977</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59611</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.01254</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34376</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.3127</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27245</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.56187</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.7997000000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57782</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65852</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.56132</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1.00156</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7913600000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.65476</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.58657</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.03385</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.38511</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5803700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.83724</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.9209299999999999</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.91944</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.77376</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.8320599999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>1.09042</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.85534</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.83158</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.6198899999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5972999999999999</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.83488</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.91415</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.97565</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.9217799999999999</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.89476</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.79334</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.90762</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.83365</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.89671</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.91373</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.90822</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.9165599999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.92857</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.9704199999999999</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.92996</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.99849</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>1.07113</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>1.0206</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>1.05829</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>1.03026</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>1.05663</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1.07319</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>1.08488</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.87321</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.93363</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.31559</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1.18971</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.23737</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1.04605</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1.03578</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.91247</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.98814</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.8162999999999999</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6726799999999999</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.5404600000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.6346000000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.75881</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.9111399999999999</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.16884</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.94516</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5664199999999999</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.13041</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8772000000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.98663</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8953</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65954</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.84497</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.10841</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.9214600000000001</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.53846</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.44031</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.91491</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.43489</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>1.32754</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.25316</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.81675</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8485</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1.16059</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.76836</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47913</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42082</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.2022</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51997</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79535</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.8073400000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.77806</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.19994</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.93991</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.6635</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.72077</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.58716</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.18252</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.64394</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.92775</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.6083500000000001</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.75877</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.68177</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.64984</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.19193</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.43184</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.55059</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.62179</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.87752</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.5376</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7693099999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.10449</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.10361</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1.01336</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1.00129</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.95525</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.19163</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.19655</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8985599999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.19613</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.63985</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>1.00756</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.05102</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.19637</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.98821</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.02936</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.61687</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.96021</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.01696</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.12407</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.9216</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.90923</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.13474</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.63413</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.99602</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.03562</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.76415</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.35613</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1.20677</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1.02204</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.01919</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.91139</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.76281</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.90989</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.3437</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.03087</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.9444199999999999</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>1.02781</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.93186</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.98894</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8368099999999999</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.7402000000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1.27734</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.97893</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.54877</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.04092</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.98099</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.98425</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.9205099999999999</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1.00141</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1.20941</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>1.28823</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.98097</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.86202</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.85477</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.8644400000000001</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.72068</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.8993099999999999</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45682</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.89722</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.91042</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.9005700000000001</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.65844</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.65671</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.73773</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1.24573</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.08634</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1.07954</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1.09285</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1.1037</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.91969</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.98799</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.7684099999999999</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.76976</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>1.05456</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>1.11274</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>1.08614</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1.02953</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.9262400000000001</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.9393899999999999</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.86013</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26679</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47468</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48794</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60703</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62613</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84626</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26649</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16199</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8495</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42843</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.6996599999999999</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9371900000000001</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16376</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.11781</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01447</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54092</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49685</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42635</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56692</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.8763300000000001</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.8734400000000001</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.87634</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.8021699999999999</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1.10007</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.62448</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.80369</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.62636</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.79765</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.9000199999999999</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>1.09283</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.92316</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.9966799999999999</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.5564600000000001</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.90078</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.54222</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.00539</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.99412</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.99571</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.55956</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55423</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9428300000000001</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08253</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.79481</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.00954</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77882</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65936</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.65209</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.7194</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79561</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29298</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.76339</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.35053</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.4884</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.16434</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.65654</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63479</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66842</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.68179</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67686</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.65385</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67834</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20669</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.71128</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.79305</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70856</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71634</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72449</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.64313</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75878</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01794</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12717</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.7024</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.71083</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.70461</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78423</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.73439</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8234400000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6739400000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46582</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.50949</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.8813200000000001</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.87185</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.90549</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34515</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.86629</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.01726</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.60681</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.8921399999999999</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1.10189</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.9061</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.87859</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1.17529</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1.1031</v>
+      </c>
+      <c r="P130" t="n">
+        <v>1.1104</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.9306599999999999</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.85738</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42757</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75648</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49557</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51481</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.5234099999999999</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45397</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.93292</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48651</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.19348</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.89938</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7609400000000001</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45782</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.50124</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.4924</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3732200000000001</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.85529</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.43685</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.45151</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75606</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5192899999999999</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.71064</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49964</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42329</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56598</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.67135</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83157</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47207</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.93789</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.9029400000000001</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.8980199999999999</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.88632</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.74364</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.66873</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.54126</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.5908</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.53603</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43867</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51546</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5439400000000001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.75912</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76554</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54306</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7186399999999999</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.75966</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55241</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50066</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01688</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48014</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44114</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.08973</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.1257</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.07845</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.10998</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12669</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.0167</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19242</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.1407</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.12953</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17622</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84202</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.1902</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84788</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.33958</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90028</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.69724</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75512</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94604</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.77879</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.9570599999999999</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.94601</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>1.12258</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.8009299999999999</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7617699999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.42977</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.93203</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.36837</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1.35039</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.9448200000000001</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.92713</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1.24334</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1.25911</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1.27248</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.9747100000000001</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1.32843</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.95155</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.27572</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.8324199999999999</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.7276900000000001</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.7268600000000001</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.72682</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.8389500000000001</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.5402899999999999</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.67971</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.48503</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.92545</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.72273</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.67989</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>1.1185</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.81028</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.14458</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.76998</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.30803</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.3681</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.75296</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.67435</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.37735</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00908</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.61887</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.50362</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.6045900000000001</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.75891</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.21099</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.71199</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.94945</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.68729</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9712799999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.91462</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.77179</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.74165</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18974</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.19092</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.46055</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.27529</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.68472</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.2665</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29804</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.12739</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.4512</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.04494</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>1.36681</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>1.25359</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.47146</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.58692</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.67848</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.5079</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48972</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5346900000000001</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5359700000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.79835</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.69059</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.5018</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.09283</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.70186</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66616</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.8051200000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.09515</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.20549</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.5004700000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.20127</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54701</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.16148</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55772</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5704199999999999</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23518</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42935</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48396</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.46443</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50941</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51084</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46028</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43404</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5452100000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.52355</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.61095</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.76306</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.14406</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.1083</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1.03271</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.57868</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.49965</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.47496</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.50406</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46629</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44704</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59468</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.55764</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45176</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46211</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46995</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.95627</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.89223</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.8969400000000001</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.91552</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.8766</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.61656</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.5274800000000001</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.43704</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.28538</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.62273</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.96768</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.61764</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.5962499999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.8581799999999999</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.85184</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.84677</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.84645</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23513</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.17196</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.75376</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.23303</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27883</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.15889</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.46415</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.70448</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5720700000000001</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.50341</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>1.10917</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.49507</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.8115399999999999</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46915</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49344</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10764</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.39438</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.62782</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.43377</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52798</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7644500000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.76467</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51706</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.43076</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44716</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.56196</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42889</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.92653</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1.00857</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.80736</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45651</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.76379</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.53249</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.71466</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.71801</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.25566</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.10004</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.00084</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.33118</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.64736</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.55502</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.50084</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5874199999999999</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7659199999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.55313</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.24632</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.76983</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.76662</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5892000000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45489</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.50134</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.02562</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.77806</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.63266</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.76577</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.21859</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6124400000000001</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.76152</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.64615</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.28179</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.91374</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.89758</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.91764</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.93621</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.6564099999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.97188</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.7015399999999999</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9982000000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.67642</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.69553</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.77057</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.6769</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.27347</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04974</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.03882</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.04662</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.5636</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.37549</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.06347</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.76306</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34567</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.56112</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.81053</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.55423</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75976</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.76161</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.56392</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.46121</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.43017</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5984299999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.56737</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45478</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48543</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50266</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.56198</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8147300000000001</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.13968</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.05257</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.14242</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.7605</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.75524</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.06342</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.08177</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.69068</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55422</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56064</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5660299999999999</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.48127</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.49307</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5515599999999999</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5501900000000001</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5494600000000001</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.6643600000000001</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.56254</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.05639</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.66704</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.55172</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.50142</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.5015299999999999</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48405</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.50132</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48362</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.50145</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.58012</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55949</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.56333</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49953</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51554</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.50195</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5634</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.66406</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.18579</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.08948</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.66444</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58562</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.17188</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.87485</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.1738</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.84899</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49932</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51332</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.5006499999999999</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53672</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34463</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.5023</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.99842</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.00657</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.78895</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1.03636</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.55952</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.46498</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5928300000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.44087</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.64819</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.04316</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.23444</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9384400000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.99787</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.04477</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.98887</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.95669</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.9875900000000001</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.97002</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9552200000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9577599999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.57751</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>1.09733</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.47919</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.47479</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.55315</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.53501</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.7410099999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.96004</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8798400000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.94682</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.5529</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.70175</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.7241</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.77245</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.21746</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.09771</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.03752</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.42601</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.34898</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.03295</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.13179</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.76998</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.76913</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.82768</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.71275</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6904</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55916</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69437</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.74773</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.70623</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7662</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.7164400000000001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46748</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.75648</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.52611</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.5129</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44544</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.03669</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.93462</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.04555</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.9469500000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.05338</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.03621</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.0364</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.60779</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.10663</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.53339</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.89801</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.68724</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.6359199999999999</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.72899</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02203</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.73212</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.78514</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.15501</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.65579</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.64147</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.37524</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.81517</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.77389</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.81099</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>1.09199</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.58048</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.76274</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.48137</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.50082</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.80836</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.30839</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00048</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9305800000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.95682</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03723</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16471</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.0739</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8608300000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6918099999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.24442</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21586</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21736</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86282</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.6999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09085</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.1028</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.1029</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13243</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10051</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.51885</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.19596</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.6646299999999999</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.58757</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15287</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.75544</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.68592</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18036</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8780399999999999</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.01606</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.0231</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.03815</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.0396</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06551</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12375</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04699</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05759</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18194</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16103</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.08777</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20072</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.31079</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16676</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.09952</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11639</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09701</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12323</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17284</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19014</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.1706</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.12613</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.69621</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6316499999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57925</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5591799999999999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37557</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.55167</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.30886</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.30646</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06427</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48217</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51906</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.66964</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.56521</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.5694199999999999</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.63517</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.6718200000000001</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.63107</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.6528200000000001</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.62688</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.6321599999999999</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.6422899999999999</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.63402</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.61893</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.5931000000000001</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.5979</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.60407</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.58323</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84787</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.59149</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.58088</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.70704</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.72262</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.6738099999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.96214</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.77406</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.96754</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.17949</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.33536</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.48143</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.46812</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.4551</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.57899</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.27334</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85024</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.31862</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73783</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.6999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50112</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84362</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.88893</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.25669</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77644</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57902</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58687</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.6501399999999999</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.73385</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.61346</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.75795</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.63295</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.2218</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.19532</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.42044</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.19757</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.1921</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.19989</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.13569</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.10977</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20672</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.13647</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.22253</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.08419</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.11292</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20567</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.12008</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.55677</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.81145</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80362</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5638099999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.23833</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84861</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84911</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55883</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5543400000000001</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56312</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5152899999999999</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55369</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52098</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50107</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45959</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45983</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49481</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49891</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5472100000000001</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.51962</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.51998</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5568500000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17459</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88225</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49236</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.21318</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50765</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.57013</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84478</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7957799999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5972499999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85156</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50592</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52064</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5462899999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17553</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70028</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55423</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.18503</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.5481900000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.54869</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58008</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79883</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55371</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7964</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8482799999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17306</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7978099999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6829500000000001</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.09778</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17488</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.18113</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.18589</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.18365</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8213400000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73633</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.65761</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.68811</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.69685</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7343</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83248</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8159400000000001</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.62387</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7673</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.14656</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.77225</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6087400000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.65576</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.64903</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6215000000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.6167699999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.72561</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.68145</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.83321</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.7037100000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60791</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53085</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51234</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
